--- a/ESP32 Project/RevisedJollyHelmet_Checked.xlsx
+++ b/ESP32 Project/RevisedJollyHelmet_Checked.xlsx
@@ -2161,27 +2161,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="40" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="20" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2208,6 +2187,27 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="20" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2552,55 +2552,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="103"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="96"/>
       <c r="M1" s="43"/>
-      <c r="N1" s="101" t="s">
+      <c r="N1" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="103"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
+      <c r="W1" s="96"/>
       <c r="X1" s="43"/>
       <c r="Y1" s="43"/>
-      <c r="Z1" s="101" t="s">
+      <c r="Z1" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="102"/>
-      <c r="AC1" s="102"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="102"/>
-      <c r="AF1" s="102"/>
-      <c r="AG1" s="102"/>
-      <c r="AH1" s="102"/>
-      <c r="AI1" s="103"/>
+      <c r="AA1" s="95"/>
+      <c r="AB1" s="95"/>
+      <c r="AC1" s="95"/>
+      <c r="AD1" s="95"/>
+      <c r="AE1" s="95"/>
+      <c r="AF1" s="95"/>
+      <c r="AG1" s="95"/>
+      <c r="AH1" s="95"/>
+      <c r="AI1" s="96"/>
       <c r="AJ1" s="43"/>
       <c r="AK1" s="14"/>
     </row>
     <row r="2" spans="2:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="109"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="102"/>
       <c r="H2" s="34" t="s">
         <v>92</v>
       </c>
@@ -2614,12 +2614,12 @@
         <v>34</v>
       </c>
       <c r="M2" s="43"/>
-      <c r="N2" s="107" t="s">
+      <c r="N2" s="100" t="s">
         <v>80</v>
       </c>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="109"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="102"/>
       <c r="R2" s="43"/>
       <c r="S2" s="43"/>
       <c r="T2" s="34" t="s">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="X2" s="43"/>
       <c r="Y2" s="43"/>
-      <c r="Z2" s="107" t="s">
+      <c r="Z2" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="AA2" s="108"/>
-      <c r="AB2" s="108"/>
-      <c r="AC2" s="109"/>
+      <c r="AA2" s="101"/>
+      <c r="AB2" s="101"/>
+      <c r="AC2" s="102"/>
       <c r="AD2" s="43"/>
       <c r="AE2" s="43"/>
       <c r="AF2" s="34" t="s">
@@ -3568,10 +3568,10 @@
       <c r="AK16" s="14"/>
     </row>
     <row r="17" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="94" t="s">
+      <c r="B17" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="106" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="26" t="s">
@@ -3588,10 +3588,10 @@
         <v>12</v>
       </c>
       <c r="M17" s="43"/>
-      <c r="N17" s="94" t="s">
+      <c r="N17" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="O17" s="97" t="s">
+      <c r="O17" s="106" t="s">
         <v>24</v>
       </c>
       <c r="P17" s="26" t="s">
@@ -3606,10 +3606,10 @@
       <c r="W17" s="52"/>
       <c r="X17" s="43"/>
       <c r="Y17" s="43"/>
-      <c r="Z17" s="94" t="s">
+      <c r="Z17" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="AA17" s="97" t="s">
+      <c r="AA17" s="106" t="s">
         <v>24</v>
       </c>
       <c r="AB17" s="26" t="s">
@@ -3626,8 +3626,8 @@
       <c r="AK17" s="14"/>
     </row>
     <row r="18" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="95"/>
-      <c r="C18" s="98"/>
+      <c r="B18" s="104"/>
+      <c r="C18" s="107"/>
       <c r="D18" s="18" t="s">
         <v>13</v>
       </c>
@@ -3641,8 +3641,8 @@
         <v>42</v>
       </c>
       <c r="M18" s="43"/>
-      <c r="N18" s="95"/>
-      <c r="O18" s="98"/>
+      <c r="N18" s="104"/>
+      <c r="O18" s="107"/>
       <c r="P18" s="18" t="s">
         <v>13</v>
       </c>
@@ -3655,8 +3655,8 @@
       <c r="W18" s="52"/>
       <c r="X18" s="43"/>
       <c r="Y18" s="43"/>
-      <c r="Z18" s="95"/>
-      <c r="AA18" s="98"/>
+      <c r="Z18" s="104"/>
+      <c r="AA18" s="107"/>
       <c r="AB18" s="18" t="s">
         <v>13</v>
       </c>
@@ -3671,8 +3671,8 @@
       <c r="AK18" s="14"/>
     </row>
     <row r="19" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="95"/>
-      <c r="C19" s="99" t="s">
+      <c r="B19" s="104"/>
+      <c r="C19" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="18" t="s">
@@ -3684,8 +3684,8 @@
       <c r="J19" s="52"/>
       <c r="K19" s="54"/>
       <c r="M19" s="43"/>
-      <c r="N19" s="95"/>
-      <c r="O19" s="99" t="s">
+      <c r="N19" s="104"/>
+      <c r="O19" s="108" t="s">
         <v>25</v>
       </c>
       <c r="P19" s="18" t="s">
@@ -3700,8 +3700,8 @@
       <c r="W19" s="52"/>
       <c r="X19" s="43"/>
       <c r="Y19" s="43"/>
-      <c r="Z19" s="95"/>
-      <c r="AA19" s="99" t="s">
+      <c r="Z19" s="104"/>
+      <c r="AA19" s="108" t="s">
         <v>25</v>
       </c>
       <c r="AB19" s="18" t="s">
@@ -3718,8 +3718,8 @@
       <c r="AK19" s="14"/>
     </row>
     <row r="20" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="96"/>
-      <c r="C20" s="100"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="109"/>
       <c r="D20" s="27" t="s">
         <v>23</v>
       </c>
@@ -3729,8 +3729,8 @@
       <c r="J20" s="52"/>
       <c r="K20" s="54"/>
       <c r="M20" s="43"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="100"/>
+      <c r="N20" s="105"/>
+      <c r="O20" s="109"/>
       <c r="P20" s="27" t="s">
         <v>23</v>
       </c>
@@ -3743,8 +3743,8 @@
       <c r="W20" s="52"/>
       <c r="X20" s="43"/>
       <c r="Y20" s="43"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="100"/>
+      <c r="Z20" s="105"/>
+      <c r="AA20" s="109"/>
       <c r="AB20" s="27" t="s">
         <v>23</v>
       </c>
@@ -4348,32 +4348,32 @@
       <c r="AK34" s="14"/>
     </row>
     <row r="35" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="101" t="s">
+      <c r="B35" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="102"/>
-      <c r="D35" s="102"/>
-      <c r="E35" s="102"/>
-      <c r="F35" s="102"/>
-      <c r="G35" s="102"/>
-      <c r="H35" s="102"/>
-      <c r="I35" s="102"/>
-      <c r="J35" s="102"/>
-      <c r="K35" s="103"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="95"/>
+      <c r="E35" s="95"/>
+      <c r="F35" s="95"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
+      <c r="I35" s="95"/>
+      <c r="J35" s="95"/>
+      <c r="K35" s="96"/>
       <c r="L35" s="43"/>
       <c r="M35" s="43"/>
-      <c r="N35" s="101" t="s">
+      <c r="N35" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="O35" s="102"/>
-      <c r="P35" s="102"/>
-      <c r="Q35" s="102"/>
-      <c r="R35" s="102"/>
-      <c r="S35" s="102"/>
-      <c r="T35" s="102"/>
-      <c r="U35" s="102"/>
-      <c r="V35" s="102"/>
-      <c r="W35" s="103"/>
+      <c r="O35" s="95"/>
+      <c r="P35" s="95"/>
+      <c r="Q35" s="95"/>
+      <c r="R35" s="95"/>
+      <c r="S35" s="95"/>
+      <c r="T35" s="95"/>
+      <c r="U35" s="95"/>
+      <c r="V35" s="95"/>
+      <c r="W35" s="96"/>
       <c r="X35" s="43"/>
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
@@ -4390,12 +4390,12 @@
       <c r="AK35" s="14"/>
     </row>
     <row r="36" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="104" t="s">
+      <c r="B36" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="105"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="106"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="98"/>
+      <c r="E36" s="99"/>
       <c r="H36" s="34" t="s">
         <v>92</v>
       </c>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L36" s="43"/>
       <c r="M36" s="43"/>
-      <c r="N36" s="107" t="s">
+      <c r="N36" s="100" t="s">
         <v>139</v>
       </c>
-      <c r="O36" s="108"/>
-      <c r="P36" s="108"/>
-      <c r="Q36" s="109"/>
+      <c r="O36" s="101"/>
+      <c r="P36" s="101"/>
+      <c r="Q36" s="102"/>
       <c r="R36" s="43"/>
       <c r="S36" s="43"/>
       <c r="T36" s="34" t="s">
@@ -5067,10 +5067,10 @@
       <c r="AK50" s="14"/>
     </row>
     <row r="51" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="94" t="s">
+      <c r="B51" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="97" t="s">
+      <c r="C51" s="106" t="s">
         <v>24</v>
       </c>
       <c r="D51" s="26" t="s">
@@ -5083,10 +5083,10 @@
       <c r="K51" s="15"/>
       <c r="L51" s="43"/>
       <c r="M51" s="43"/>
-      <c r="N51" s="94" t="s">
+      <c r="N51" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="O51" s="97" t="s">
+      <c r="O51" s="106" t="s">
         <v>24</v>
       </c>
       <c r="P51" s="26" t="s">
@@ -5115,8 +5115,8 @@
       <c r="AK51" s="14"/>
     </row>
     <row r="52" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="95"/>
-      <c r="C52" s="98"/>
+      <c r="B52" s="104"/>
+      <c r="C52" s="107"/>
       <c r="D52" s="18" t="s">
         <v>13</v>
       </c>
@@ -5127,8 +5127,8 @@
       <c r="K52" s="15"/>
       <c r="L52" s="43"/>
       <c r="M52" s="43"/>
-      <c r="N52" s="95"/>
-      <c r="O52" s="98"/>
+      <c r="N52" s="104"/>
+      <c r="O52" s="107"/>
       <c r="P52" s="18" t="s">
         <v>13</v>
       </c>
@@ -5155,8 +5155,8 @@
       <c r="AK52" s="14"/>
     </row>
     <row r="53" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="95"/>
-      <c r="C53" s="99" t="s">
+      <c r="B53" s="104"/>
+      <c r="C53" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D53" s="18" t="s">
@@ -5169,8 +5169,8 @@
       <c r="K53" s="15"/>
       <c r="L53" s="43"/>
       <c r="M53" s="43"/>
-      <c r="N53" s="95"/>
-      <c r="O53" s="99" t="s">
+      <c r="N53" s="104"/>
+      <c r="O53" s="108" t="s">
         <v>25</v>
       </c>
       <c r="P53" s="18" t="s">
@@ -5199,8 +5199,8 @@
       <c r="AK53" s="14"/>
     </row>
     <row r="54" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="96"/>
-      <c r="C54" s="100"/>
+      <c r="B54" s="105"/>
+      <c r="C54" s="109"/>
       <c r="D54" s="27" t="s">
         <v>23</v>
       </c>
@@ -5211,8 +5211,8 @@
       <c r="K54" s="15"/>
       <c r="L54" s="43"/>
       <c r="M54" s="43"/>
-      <c r="N54" s="96"/>
-      <c r="O54" s="100"/>
+      <c r="N54" s="105"/>
+      <c r="O54" s="109"/>
       <c r="P54" s="27" t="s">
         <v>23</v>
       </c>
@@ -5794,32 +5794,32 @@
     </row>
     <row r="69" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="43"/>
-      <c r="B69" s="101" t="s">
+      <c r="B69" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="C69" s="102"/>
-      <c r="D69" s="102"/>
-      <c r="E69" s="102"/>
-      <c r="F69" s="102"/>
-      <c r="G69" s="102"/>
-      <c r="H69" s="102"/>
-      <c r="I69" s="102"/>
-      <c r="J69" s="102"/>
-      <c r="K69" s="103"/>
+      <c r="C69" s="95"/>
+      <c r="D69" s="95"/>
+      <c r="E69" s="95"/>
+      <c r="F69" s="95"/>
+      <c r="G69" s="95"/>
+      <c r="H69" s="95"/>
+      <c r="I69" s="95"/>
+      <c r="J69" s="95"/>
+      <c r="K69" s="96"/>
       <c r="L69" s="43"/>
       <c r="M69" s="43"/>
-      <c r="N69" s="101" t="s">
+      <c r="N69" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="O69" s="102"/>
-      <c r="P69" s="102"/>
-      <c r="Q69" s="102"/>
-      <c r="R69" s="102"/>
-      <c r="S69" s="102"/>
-      <c r="T69" s="102"/>
-      <c r="U69" s="102"/>
-      <c r="V69" s="102"/>
-      <c r="W69" s="103"/>
+      <c r="O69" s="95"/>
+      <c r="P69" s="95"/>
+      <c r="Q69" s="95"/>
+      <c r="R69" s="95"/>
+      <c r="S69" s="95"/>
+      <c r="T69" s="95"/>
+      <c r="U69" s="95"/>
+      <c r="V69" s="95"/>
+      <c r="W69" s="96"/>
       <c r="X69" s="43"/>
       <c r="Y69" s="14"/>
       <c r="Z69" s="14"/>
@@ -5837,12 +5837,12 @@
     </row>
     <row r="70" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="43"/>
-      <c r="B70" s="104" t="s">
+      <c r="B70" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="C70" s="105"/>
-      <c r="D70" s="105"/>
-      <c r="E70" s="106"/>
+      <c r="C70" s="98"/>
+      <c r="D70" s="98"/>
+      <c r="E70" s="99"/>
       <c r="F70" s="43"/>
       <c r="G70" s="43"/>
       <c r="H70" s="34" t="s">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="L70" s="43"/>
       <c r="M70" s="43"/>
-      <c r="N70" s="107" t="s">
+      <c r="N70" s="100" t="s">
         <v>91</v>
       </c>
-      <c r="O70" s="108"/>
-      <c r="P70" s="108"/>
-      <c r="Q70" s="109"/>
+      <c r="O70" s="101"/>
+      <c r="P70" s="101"/>
+      <c r="Q70" s="102"/>
       <c r="R70" s="43"/>
       <c r="S70" s="43"/>
       <c r="T70" s="34" t="s">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="85" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="43"/>
-      <c r="B85" s="94" t="s">
+      <c r="B85" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="C85" s="97" t="s">
+      <c r="C85" s="106" t="s">
         <v>24</v>
       </c>
       <c r="D85" s="26" t="s">
@@ -6760,10 +6760,10 @@
       </c>
       <c r="L85" s="43"/>
       <c r="M85" s="43"/>
-      <c r="N85" s="94" t="s">
+      <c r="N85" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="O85" s="97" t="s">
+      <c r="O85" s="106" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="26" t="s">
@@ -6793,8 +6793,8 @@
     </row>
     <row r="86" spans="1:37" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="43"/>
-      <c r="B86" s="95"/>
-      <c r="C86" s="98"/>
+      <c r="B86" s="104"/>
+      <c r="C86" s="107"/>
       <c r="D86" s="18" t="s">
         <v>13</v>
       </c>
@@ -6811,8 +6811,8 @@
       </c>
       <c r="L86" s="43"/>
       <c r="M86" s="43"/>
-      <c r="N86" s="95"/>
-      <c r="O86" s="98"/>
+      <c r="N86" s="104"/>
+      <c r="O86" s="107"/>
       <c r="P86" s="18" t="s">
         <v>13</v>
       </c>
@@ -6840,8 +6840,8 @@
     </row>
     <row r="87" spans="1:37" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="43"/>
-      <c r="B87" s="95"/>
-      <c r="C87" s="99" t="s">
+      <c r="B87" s="104"/>
+      <c r="C87" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D87" s="18" t="s">
@@ -6856,8 +6856,8 @@
       <c r="K87" s="54"/>
       <c r="L87" s="43"/>
       <c r="M87" s="43"/>
-      <c r="N87" s="95"/>
-      <c r="O87" s="99" t="s">
+      <c r="N87" s="104"/>
+      <c r="O87" s="108" t="s">
         <v>25</v>
       </c>
       <c r="P87" s="18" t="s">
@@ -6887,8 +6887,8 @@
     </row>
     <row r="88" spans="1:37" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="43"/>
-      <c r="B88" s="96"/>
-      <c r="C88" s="100"/>
+      <c r="B88" s="105"/>
+      <c r="C88" s="109"/>
       <c r="D88" s="27" t="s">
         <v>23</v>
       </c>
@@ -6901,8 +6901,8 @@
       <c r="K88" s="54"/>
       <c r="L88" s="43"/>
       <c r="M88" s="43"/>
-      <c r="N88" s="96"/>
-      <c r="O88" s="100"/>
+      <c r="N88" s="105"/>
+      <c r="O88" s="109"/>
       <c r="P88" s="27" t="s">
         <v>23</v>
       </c>
@@ -7512,57 +7512,57 @@
     </row>
     <row r="103" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="43"/>
-      <c r="B103" s="101" t="s">
+      <c r="B103" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="C103" s="102"/>
-      <c r="D103" s="102"/>
-      <c r="E103" s="102"/>
-      <c r="F103" s="102"/>
-      <c r="G103" s="102"/>
-      <c r="H103" s="102"/>
-      <c r="I103" s="102"/>
-      <c r="J103" s="102"/>
-      <c r="K103" s="103"/>
+      <c r="C103" s="95"/>
+      <c r="D103" s="95"/>
+      <c r="E103" s="95"/>
+      <c r="F103" s="95"/>
+      <c r="G103" s="95"/>
+      <c r="H103" s="95"/>
+      <c r="I103" s="95"/>
+      <c r="J103" s="95"/>
+      <c r="K103" s="96"/>
       <c r="L103" s="43"/>
       <c r="M103" s="43"/>
-      <c r="N103" s="101" t="s">
+      <c r="N103" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="O103" s="102"/>
-      <c r="P103" s="102"/>
-      <c r="Q103" s="102"/>
-      <c r="R103" s="102"/>
-      <c r="S103" s="102"/>
-      <c r="T103" s="102"/>
-      <c r="U103" s="102"/>
-      <c r="V103" s="102"/>
-      <c r="W103" s="103"/>
+      <c r="O103" s="95"/>
+      <c r="P103" s="95"/>
+      <c r="Q103" s="95"/>
+      <c r="R103" s="95"/>
+      <c r="S103" s="95"/>
+      <c r="T103" s="95"/>
+      <c r="U103" s="95"/>
+      <c r="V103" s="95"/>
+      <c r="W103" s="96"/>
       <c r="X103" s="43"/>
       <c r="Y103" s="43"/>
-      <c r="Z103" s="101" t="s">
+      <c r="Z103" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="AA103" s="102"/>
-      <c r="AB103" s="102"/>
-      <c r="AC103" s="102"/>
-      <c r="AD103" s="102"/>
-      <c r="AE103" s="102"/>
-      <c r="AF103" s="102"/>
-      <c r="AG103" s="102"/>
-      <c r="AH103" s="102"/>
-      <c r="AI103" s="103"/>
+      <c r="AA103" s="95"/>
+      <c r="AB103" s="95"/>
+      <c r="AC103" s="95"/>
+      <c r="AD103" s="95"/>
+      <c r="AE103" s="95"/>
+      <c r="AF103" s="95"/>
+      <c r="AG103" s="95"/>
+      <c r="AH103" s="95"/>
+      <c r="AI103" s="96"/>
       <c r="AJ103" s="43"/>
       <c r="AK103" s="14"/>
     </row>
     <row r="104" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="43"/>
-      <c r="B104" s="107" t="s">
+      <c r="B104" s="100" t="s">
         <v>117</v>
       </c>
-      <c r="C104" s="108"/>
-      <c r="D104" s="108"/>
-      <c r="E104" s="109"/>
+      <c r="C104" s="101"/>
+      <c r="D104" s="101"/>
+      <c r="E104" s="102"/>
       <c r="F104" s="43"/>
       <c r="G104" s="43"/>
       <c r="H104" s="34" t="s">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="L104" s="43"/>
       <c r="M104" s="43"/>
-      <c r="N104" s="107" t="s">
+      <c r="N104" s="100" t="s">
         <v>118</v>
       </c>
-      <c r="O104" s="108"/>
-      <c r="P104" s="108"/>
-      <c r="Q104" s="109"/>
+      <c r="O104" s="101"/>
+      <c r="P104" s="101"/>
+      <c r="Q104" s="102"/>
       <c r="R104" s="43"/>
       <c r="S104" s="43"/>
       <c r="T104" s="34" t="s">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="X104" s="43"/>
       <c r="Y104" s="43"/>
-      <c r="Z104" s="107" t="s">
+      <c r="Z104" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="AA104" s="108"/>
-      <c r="AB104" s="108"/>
-      <c r="AC104" s="109"/>
+      <c r="AA104" s="101"/>
+      <c r="AB104" s="101"/>
+      <c r="AC104" s="102"/>
       <c r="AD104" s="43"/>
       <c r="AE104" s="43"/>
       <c r="AF104" s="34" t="s">
@@ -8590,10 +8590,10 @@
     </row>
     <row r="119" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="43"/>
-      <c r="B119" s="94" t="s">
+      <c r="B119" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="C119" s="97" t="s">
+      <c r="C119" s="106" t="s">
         <v>24</v>
       </c>
       <c r="D119" s="26" t="s">
@@ -8612,10 +8612,10 @@
       </c>
       <c r="L119" s="43"/>
       <c r="M119" s="43"/>
-      <c r="N119" s="94" t="s">
+      <c r="N119" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="O119" s="97" t="s">
+      <c r="O119" s="106" t="s">
         <v>24</v>
       </c>
       <c r="P119" s="26" t="s">
@@ -8630,10 +8630,10 @@
       <c r="W119" s="52"/>
       <c r="X119" s="43"/>
       <c r="Y119" s="43"/>
-      <c r="Z119" s="94" t="s">
+      <c r="Z119" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="AA119" s="97" t="s">
+      <c r="AA119" s="106" t="s">
         <v>24</v>
       </c>
       <c r="AB119" s="26" t="s">
@@ -8651,8 +8651,8 @@
     </row>
     <row r="120" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="43"/>
-      <c r="B120" s="95"/>
-      <c r="C120" s="98"/>
+      <c r="B120" s="104"/>
+      <c r="C120" s="107"/>
       <c r="D120" s="18" t="s">
         <v>13</v>
       </c>
@@ -8669,8 +8669,8 @@
       </c>
       <c r="L120" s="43"/>
       <c r="M120" s="43"/>
-      <c r="N120" s="95"/>
-      <c r="O120" s="98"/>
+      <c r="N120" s="104"/>
+      <c r="O120" s="107"/>
       <c r="P120" s="18" t="s">
         <v>13</v>
       </c>
@@ -8683,8 +8683,8 @@
       <c r="W120" s="52"/>
       <c r="X120" s="43"/>
       <c r="Y120" s="43"/>
-      <c r="Z120" s="95"/>
-      <c r="AA120" s="98"/>
+      <c r="Z120" s="104"/>
+      <c r="AA120" s="107"/>
       <c r="AB120" s="18" t="s">
         <v>13</v>
       </c>
@@ -8700,8 +8700,8 @@
     </row>
     <row r="121" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="43"/>
-      <c r="B121" s="95"/>
-      <c r="C121" s="99" t="s">
+      <c r="B121" s="104"/>
+      <c r="C121" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D121" s="18" t="s">
@@ -8716,8 +8716,8 @@
       <c r="K121" s="54"/>
       <c r="L121" s="43"/>
       <c r="M121" s="43"/>
-      <c r="N121" s="95"/>
-      <c r="O121" s="99" t="s">
+      <c r="N121" s="104"/>
+      <c r="O121" s="108" t="s">
         <v>25</v>
       </c>
       <c r="P121" s="18" t="s">
@@ -8732,8 +8732,8 @@
       <c r="W121" s="52"/>
       <c r="X121" s="43"/>
       <c r="Y121" s="43"/>
-      <c r="Z121" s="95"/>
-      <c r="AA121" s="99" t="s">
+      <c r="Z121" s="104"/>
+      <c r="AA121" s="108" t="s">
         <v>25</v>
       </c>
       <c r="AB121" s="18" t="s">
@@ -8751,8 +8751,8 @@
     </row>
     <row r="122" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="43"/>
-      <c r="B122" s="96"/>
-      <c r="C122" s="100"/>
+      <c r="B122" s="105"/>
+      <c r="C122" s="109"/>
       <c r="D122" s="27" t="s">
         <v>23</v>
       </c>
@@ -8765,8 +8765,8 @@
       <c r="K122" s="54"/>
       <c r="L122" s="43"/>
       <c r="M122" s="43"/>
-      <c r="N122" s="96"/>
-      <c r="O122" s="100"/>
+      <c r="N122" s="105"/>
+      <c r="O122" s="109"/>
       <c r="P122" s="27" t="s">
         <v>23</v>
       </c>
@@ -8779,8 +8779,8 @@
       <c r="W122" s="52"/>
       <c r="X122" s="43"/>
       <c r="Y122" s="43"/>
-      <c r="Z122" s="96"/>
-      <c r="AA122" s="100"/>
+      <c r="Z122" s="105"/>
+      <c r="AA122" s="109"/>
       <c r="AB122" s="27" t="s">
         <v>23</v>
       </c>
@@ -9396,43 +9396,43 @@
     </row>
     <row r="137" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="43"/>
-      <c r="B137" s="101" t="s">
+      <c r="B137" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="C137" s="102"/>
-      <c r="D137" s="102"/>
-      <c r="E137" s="102"/>
-      <c r="F137" s="102"/>
-      <c r="G137" s="102"/>
-      <c r="H137" s="102"/>
-      <c r="I137" s="102"/>
-      <c r="J137" s="102"/>
-      <c r="K137" s="103"/>
+      <c r="C137" s="95"/>
+      <c r="D137" s="95"/>
+      <c r="E137" s="95"/>
+      <c r="F137" s="95"/>
+      <c r="G137" s="95"/>
+      <c r="H137" s="95"/>
+      <c r="I137" s="95"/>
+      <c r="J137" s="95"/>
+      <c r="K137" s="96"/>
       <c r="L137" s="43"/>
       <c r="M137" s="43"/>
-      <c r="N137" s="101" t="s">
+      <c r="N137" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="O137" s="102"/>
-      <c r="P137" s="102"/>
-      <c r="Q137" s="102"/>
-      <c r="R137" s="102"/>
-      <c r="S137" s="102"/>
-      <c r="T137" s="102"/>
-      <c r="U137" s="102"/>
-      <c r="V137" s="102"/>
-      <c r="W137" s="103"/>
+      <c r="O137" s="95"/>
+      <c r="P137" s="95"/>
+      <c r="Q137" s="95"/>
+      <c r="R137" s="95"/>
+      <c r="S137" s="95"/>
+      <c r="T137" s="95"/>
+      <c r="U137" s="95"/>
+      <c r="V137" s="95"/>
+      <c r="W137" s="96"/>
       <c r="X137" s="43"/>
       <c r="Y137" s="14"/>
     </row>
     <row r="138" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="43"/>
-      <c r="B138" s="104" t="s">
+      <c r="B138" s="97" t="s">
         <v>131</v>
       </c>
-      <c r="C138" s="105"/>
-      <c r="D138" s="105"/>
-      <c r="E138" s="106"/>
+      <c r="C138" s="98"/>
+      <c r="D138" s="98"/>
+      <c r="E138" s="99"/>
       <c r="F138" s="43"/>
       <c r="G138" s="43"/>
       <c r="H138" s="71" t="s">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="L138" s="43"/>
       <c r="M138" s="43"/>
-      <c r="N138" s="107" t="s">
+      <c r="N138" s="100" t="s">
         <v>132</v>
       </c>
-      <c r="O138" s="108"/>
-      <c r="P138" s="108"/>
-      <c r="Q138" s="109"/>
+      <c r="O138" s="101"/>
+      <c r="P138" s="101"/>
+      <c r="Q138" s="102"/>
       <c r="R138" s="43"/>
       <c r="S138" s="43"/>
       <c r="T138" s="34" t="s">
@@ -10039,10 +10039,10 @@
     </row>
     <row r="153" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="43"/>
-      <c r="B153" s="94" t="s">
+      <c r="B153" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="C153" s="97" t="s">
+      <c r="C153" s="106" t="s">
         <v>24</v>
       </c>
       <c r="D153" s="26" t="s">
@@ -10057,10 +10057,10 @@
       <c r="K153" s="45"/>
       <c r="L153" s="43"/>
       <c r="M153" s="43"/>
-      <c r="N153" s="94" t="s">
+      <c r="N153" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="O153" s="97" t="s">
+      <c r="O153" s="106" t="s">
         <v>24</v>
       </c>
       <c r="P153" s="26" t="s">
@@ -10078,8 +10078,8 @@
     </row>
     <row r="154" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="43"/>
-      <c r="B154" s="95"/>
-      <c r="C154" s="98"/>
+      <c r="B154" s="104"/>
+      <c r="C154" s="107"/>
       <c r="D154" s="18" t="s">
         <v>13</v>
       </c>
@@ -10092,8 +10092,8 @@
       <c r="K154" s="45"/>
       <c r="L154" s="43"/>
       <c r="M154" s="43"/>
-      <c r="N154" s="95"/>
-      <c r="O154" s="98"/>
+      <c r="N154" s="104"/>
+      <c r="O154" s="107"/>
       <c r="P154" s="18" t="s">
         <v>13</v>
       </c>
@@ -10109,8 +10109,8 @@
     </row>
     <row r="155" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="43"/>
-      <c r="B155" s="95"/>
-      <c r="C155" s="99" t="s">
+      <c r="B155" s="104"/>
+      <c r="C155" s="108" t="s">
         <v>25</v>
       </c>
       <c r="D155" s="18" t="s">
@@ -10125,8 +10125,8 @@
       <c r="K155" s="45"/>
       <c r="L155" s="43"/>
       <c r="M155" s="43"/>
-      <c r="N155" s="95"/>
-      <c r="O155" s="99" t="s">
+      <c r="N155" s="104"/>
+      <c r="O155" s="108" t="s">
         <v>25</v>
       </c>
       <c r="P155" s="18" t="s">
@@ -10144,8 +10144,8 @@
     </row>
     <row r="156" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="43"/>
-      <c r="B156" s="96"/>
-      <c r="C156" s="100"/>
+      <c r="B156" s="105"/>
+      <c r="C156" s="109"/>
       <c r="D156" s="27" t="s">
         <v>23</v>
       </c>
@@ -10158,8 +10158,8 @@
       <c r="K156" s="45"/>
       <c r="L156" s="43"/>
       <c r="M156" s="43"/>
-      <c r="N156" s="96"/>
-      <c r="O156" s="100"/>
+      <c r="N156" s="105"/>
+      <c r="O156" s="109"/>
       <c r="P156" s="27" t="s">
         <v>23</v>
       </c>
@@ -10583,6 +10583,66 @@
     </row>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="H97:K97"/>
+    <mergeCell ref="T97:W97"/>
+    <mergeCell ref="B85:B88"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="N85:N88"/>
+    <mergeCell ref="O85:O86"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="O87:O88"/>
+    <mergeCell ref="T63:W63"/>
+    <mergeCell ref="B69:K69"/>
+    <mergeCell ref="N69:W69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="N70:Q70"/>
+    <mergeCell ref="H63:K63"/>
+    <mergeCell ref="N35:W35"/>
+    <mergeCell ref="N36:Q36"/>
+    <mergeCell ref="N51:N54"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="Z1:AI1"/>
+    <mergeCell ref="T29:W29"/>
+    <mergeCell ref="N1:W1"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="N17:N20"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="AA17:AA18"/>
+    <mergeCell ref="Z17:Z20"/>
+    <mergeCell ref="Z2:AC2"/>
+    <mergeCell ref="B103:K103"/>
+    <mergeCell ref="N103:W103"/>
+    <mergeCell ref="Z103:AI103"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="N104:Q104"/>
+    <mergeCell ref="Z104:AC104"/>
+    <mergeCell ref="B119:B122"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="N119:N122"/>
+    <mergeCell ref="O119:O120"/>
+    <mergeCell ref="Z119:Z122"/>
+    <mergeCell ref="AF131:AI131"/>
+    <mergeCell ref="AA119:AA120"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="O121:O122"/>
+    <mergeCell ref="AA121:AA122"/>
+    <mergeCell ref="H131:K131"/>
+    <mergeCell ref="T131:W131"/>
     <mergeCell ref="H165:K165"/>
     <mergeCell ref="T165:W165"/>
     <mergeCell ref="B137:K137"/>
@@ -10595,66 +10655,6 @@
     <mergeCell ref="O153:O154"/>
     <mergeCell ref="C155:C156"/>
     <mergeCell ref="O155:O156"/>
-    <mergeCell ref="AF131:AI131"/>
-    <mergeCell ref="AA119:AA120"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="O121:O122"/>
-    <mergeCell ref="AA121:AA122"/>
-    <mergeCell ref="H131:K131"/>
-    <mergeCell ref="T131:W131"/>
-    <mergeCell ref="B119:B122"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="N119:N122"/>
-    <mergeCell ref="O119:O120"/>
-    <mergeCell ref="Z119:Z122"/>
-    <mergeCell ref="B103:K103"/>
-    <mergeCell ref="N103:W103"/>
-    <mergeCell ref="Z103:AI103"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="N104:Q104"/>
-    <mergeCell ref="Z104:AC104"/>
-    <mergeCell ref="Z1:AI1"/>
-    <mergeCell ref="T29:W29"/>
-    <mergeCell ref="N1:W1"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="N17:N20"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="AA19:AA20"/>
-    <mergeCell ref="AA17:AA18"/>
-    <mergeCell ref="Z17:Z20"/>
-    <mergeCell ref="Z2:AC2"/>
-    <mergeCell ref="B35:K35"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="N35:W35"/>
-    <mergeCell ref="N36:Q36"/>
-    <mergeCell ref="N51:N54"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="T63:W63"/>
-    <mergeCell ref="B69:K69"/>
-    <mergeCell ref="N69:W69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="N70:Q70"/>
-    <mergeCell ref="H63:K63"/>
-    <mergeCell ref="H97:K97"/>
-    <mergeCell ref="T97:W97"/>
-    <mergeCell ref="B85:B88"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="N85:N88"/>
-    <mergeCell ref="O85:O86"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="O87:O88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/ESP32 Project/RevisedJollyHelmet_Checked.xlsx
+++ b/ESP32 Project/RevisedJollyHelmet_Checked.xlsx
@@ -2161,6 +2161,27 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="40" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="20" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2187,27 +2208,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="20" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2552,55 +2552,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="96"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="103"/>
       <c r="M1" s="43"/>
-      <c r="N1" s="94" t="s">
+      <c r="N1" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
-      <c r="W1" s="96"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="103"/>
       <c r="X1" s="43"/>
       <c r="Y1" s="43"/>
-      <c r="Z1" s="94" t="s">
+      <c r="Z1" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="AA1" s="95"/>
-      <c r="AB1" s="95"/>
-      <c r="AC1" s="95"/>
-      <c r="AD1" s="95"/>
-      <c r="AE1" s="95"/>
-      <c r="AF1" s="95"/>
-      <c r="AG1" s="95"/>
-      <c r="AH1" s="95"/>
-      <c r="AI1" s="96"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="102"/>
+      <c r="AG1" s="102"/>
+      <c r="AH1" s="102"/>
+      <c r="AI1" s="103"/>
       <c r="AJ1" s="43"/>
       <c r="AK1" s="14"/>
     </row>
     <row r="2" spans="2:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="100" t="s">
+      <c r="B2" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="102"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="109"/>
       <c r="H2" s="34" t="s">
         <v>92</v>
       </c>
@@ -2614,12 +2614,12 @@
         <v>34</v>
       </c>
       <c r="M2" s="43"/>
-      <c r="N2" s="100" t="s">
+      <c r="N2" s="107" t="s">
         <v>80</v>
       </c>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="102"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="108"/>
+      <c r="Q2" s="109"/>
       <c r="R2" s="43"/>
       <c r="S2" s="43"/>
       <c r="T2" s="34" t="s">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="X2" s="43"/>
       <c r="Y2" s="43"/>
-      <c r="Z2" s="100" t="s">
+      <c r="Z2" s="107" t="s">
         <v>105</v>
       </c>
-      <c r="AA2" s="101"/>
-      <c r="AB2" s="101"/>
-      <c r="AC2" s="102"/>
+      <c r="AA2" s="108"/>
+      <c r="AB2" s="108"/>
+      <c r="AC2" s="109"/>
       <c r="AD2" s="43"/>
       <c r="AE2" s="43"/>
       <c r="AF2" s="34" t="s">
@@ -3568,10 +3568,10 @@
       <c r="AK16" s="14"/>
     </row>
     <row r="17" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="103" t="s">
+      <c r="B17" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="106" t="s">
+      <c r="C17" s="97" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="26" t="s">
@@ -3588,10 +3588,10 @@
         <v>12</v>
       </c>
       <c r="M17" s="43"/>
-      <c r="N17" s="103" t="s">
+      <c r="N17" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="O17" s="106" t="s">
+      <c r="O17" s="97" t="s">
         <v>24</v>
       </c>
       <c r="P17" s="26" t="s">
@@ -3606,10 +3606,10 @@
       <c r="W17" s="52"/>
       <c r="X17" s="43"/>
       <c r="Y17" s="43"/>
-      <c r="Z17" s="103" t="s">
+      <c r="Z17" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="AA17" s="106" t="s">
+      <c r="AA17" s="97" t="s">
         <v>24</v>
       </c>
       <c r="AB17" s="26" t="s">
@@ -3626,8 +3626,8 @@
       <c r="AK17" s="14"/>
     </row>
     <row r="18" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="104"/>
-      <c r="C18" s="107"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="98"/>
       <c r="D18" s="18" t="s">
         <v>13</v>
       </c>
@@ -3641,8 +3641,8 @@
         <v>42</v>
       </c>
       <c r="M18" s="43"/>
-      <c r="N18" s="104"/>
-      <c r="O18" s="107"/>
+      <c r="N18" s="95"/>
+      <c r="O18" s="98"/>
       <c r="P18" s="18" t="s">
         <v>13</v>
       </c>
@@ -3655,8 +3655,8 @@
       <c r="W18" s="52"/>
       <c r="X18" s="43"/>
       <c r="Y18" s="43"/>
-      <c r="Z18" s="104"/>
-      <c r="AA18" s="107"/>
+      <c r="Z18" s="95"/>
+      <c r="AA18" s="98"/>
       <c r="AB18" s="18" t="s">
         <v>13</v>
       </c>
@@ -3671,8 +3671,8 @@
       <c r="AK18" s="14"/>
     </row>
     <row r="19" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="104"/>
-      <c r="C19" s="108" t="s">
+      <c r="B19" s="95"/>
+      <c r="C19" s="99" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="18" t="s">
@@ -3684,8 +3684,8 @@
       <c r="J19" s="52"/>
       <c r="K19" s="54"/>
       <c r="M19" s="43"/>
-      <c r="N19" s="104"/>
-      <c r="O19" s="108" t="s">
+      <c r="N19" s="95"/>
+      <c r="O19" s="99" t="s">
         <v>25</v>
       </c>
       <c r="P19" s="18" t="s">
@@ -3700,8 +3700,8 @@
       <c r="W19" s="52"/>
       <c r="X19" s="43"/>
       <c r="Y19" s="43"/>
-      <c r="Z19" s="104"/>
-      <c r="AA19" s="108" t="s">
+      <c r="Z19" s="95"/>
+      <c r="AA19" s="99" t="s">
         <v>25</v>
       </c>
       <c r="AB19" s="18" t="s">
@@ -3718,8 +3718,8 @@
       <c r="AK19" s="14"/>
     </row>
     <row r="20" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="105"/>
-      <c r="C20" s="109"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="100"/>
       <c r="D20" s="27" t="s">
         <v>23</v>
       </c>
@@ -3729,8 +3729,8 @@
       <c r="J20" s="52"/>
       <c r="K20" s="54"/>
       <c r="M20" s="43"/>
-      <c r="N20" s="105"/>
-      <c r="O20" s="109"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="100"/>
       <c r="P20" s="27" t="s">
         <v>23</v>
       </c>
@@ -3743,8 +3743,8 @@
       <c r="W20" s="52"/>
       <c r="X20" s="43"/>
       <c r="Y20" s="43"/>
-      <c r="Z20" s="105"/>
-      <c r="AA20" s="109"/>
+      <c r="Z20" s="96"/>
+      <c r="AA20" s="100"/>
       <c r="AB20" s="27" t="s">
         <v>23</v>
       </c>
@@ -4348,32 +4348,32 @@
       <c r="AK34" s="14"/>
     </row>
     <row r="35" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="94" t="s">
+      <c r="B35" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="95"/>
-      <c r="D35" s="95"/>
-      <c r="E35" s="95"/>
-      <c r="F35" s="95"/>
-      <c r="G35" s="95"/>
-      <c r="H35" s="95"/>
-      <c r="I35" s="95"/>
-      <c r="J35" s="95"/>
-      <c r="K35" s="96"/>
+      <c r="C35" s="102"/>
+      <c r="D35" s="102"/>
+      <c r="E35" s="102"/>
+      <c r="F35" s="102"/>
+      <c r="G35" s="102"/>
+      <c r="H35" s="102"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="102"/>
+      <c r="K35" s="103"/>
       <c r="L35" s="43"/>
       <c r="M35" s="43"/>
-      <c r="N35" s="94" t="s">
+      <c r="N35" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="O35" s="95"/>
-      <c r="P35" s="95"/>
-      <c r="Q35" s="95"/>
-      <c r="R35" s="95"/>
-      <c r="S35" s="95"/>
-      <c r="T35" s="95"/>
-      <c r="U35" s="95"/>
-      <c r="V35" s="95"/>
-      <c r="W35" s="96"/>
+      <c r="O35" s="102"/>
+      <c r="P35" s="102"/>
+      <c r="Q35" s="102"/>
+      <c r="R35" s="102"/>
+      <c r="S35" s="102"/>
+      <c r="T35" s="102"/>
+      <c r="U35" s="102"/>
+      <c r="V35" s="102"/>
+      <c r="W35" s="103"/>
       <c r="X35" s="43"/>
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
@@ -4390,12 +4390,12 @@
       <c r="AK35" s="14"/>
     </row>
     <row r="36" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="97" t="s">
+      <c r="B36" s="104" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="98"/>
-      <c r="D36" s="98"/>
-      <c r="E36" s="99"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="106"/>
       <c r="H36" s="34" t="s">
         <v>92</v>
       </c>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L36" s="43"/>
       <c r="M36" s="43"/>
-      <c r="N36" s="100" t="s">
+      <c r="N36" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="O36" s="101"/>
-      <c r="P36" s="101"/>
-      <c r="Q36" s="102"/>
+      <c r="O36" s="108"/>
+      <c r="P36" s="108"/>
+      <c r="Q36" s="109"/>
       <c r="R36" s="43"/>
       <c r="S36" s="43"/>
       <c r="T36" s="34" t="s">
@@ -5067,10 +5067,10 @@
       <c r="AK50" s="14"/>
     </row>
     <row r="51" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="103" t="s">
+      <c r="B51" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="106" t="s">
+      <c r="C51" s="97" t="s">
         <v>24</v>
       </c>
       <c r="D51" s="26" t="s">
@@ -5083,10 +5083,10 @@
       <c r="K51" s="15"/>
       <c r="L51" s="43"/>
       <c r="M51" s="43"/>
-      <c r="N51" s="103" t="s">
+      <c r="N51" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="O51" s="106" t="s">
+      <c r="O51" s="97" t="s">
         <v>24</v>
       </c>
       <c r="P51" s="26" t="s">
@@ -5115,8 +5115,8 @@
       <c r="AK51" s="14"/>
     </row>
     <row r="52" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="104"/>
-      <c r="C52" s="107"/>
+      <c r="B52" s="95"/>
+      <c r="C52" s="98"/>
       <c r="D52" s="18" t="s">
         <v>13</v>
       </c>
@@ -5127,8 +5127,8 @@
       <c r="K52" s="15"/>
       <c r="L52" s="43"/>
       <c r="M52" s="43"/>
-      <c r="N52" s="104"/>
-      <c r="O52" s="107"/>
+      <c r="N52" s="95"/>
+      <c r="O52" s="98"/>
       <c r="P52" s="18" t="s">
         <v>13</v>
       </c>
@@ -5155,8 +5155,8 @@
       <c r="AK52" s="14"/>
     </row>
     <row r="53" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="104"/>
-      <c r="C53" s="108" t="s">
+      <c r="B53" s="95"/>
+      <c r="C53" s="99" t="s">
         <v>25</v>
       </c>
       <c r="D53" s="18" t="s">
@@ -5169,8 +5169,8 @@
       <c r="K53" s="15"/>
       <c r="L53" s="43"/>
       <c r="M53" s="43"/>
-      <c r="N53" s="104"/>
-      <c r="O53" s="108" t="s">
+      <c r="N53" s="95"/>
+      <c r="O53" s="99" t="s">
         <v>25</v>
       </c>
       <c r="P53" s="18" t="s">
@@ -5199,8 +5199,8 @@
       <c r="AK53" s="14"/>
     </row>
     <row r="54" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="105"/>
-      <c r="C54" s="109"/>
+      <c r="B54" s="96"/>
+      <c r="C54" s="100"/>
       <c r="D54" s="27" t="s">
         <v>23</v>
       </c>
@@ -5211,8 +5211,8 @@
       <c r="K54" s="15"/>
       <c r="L54" s="43"/>
       <c r="M54" s="43"/>
-      <c r="N54" s="105"/>
-      <c r="O54" s="109"/>
+      <c r="N54" s="96"/>
+      <c r="O54" s="100"/>
       <c r="P54" s="27" t="s">
         <v>23</v>
       </c>
@@ -5794,32 +5794,32 @@
     </row>
     <row r="69" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="43"/>
-      <c r="B69" s="94" t="s">
+      <c r="B69" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="C69" s="95"/>
-      <c r="D69" s="95"/>
-      <c r="E69" s="95"/>
-      <c r="F69" s="95"/>
-      <c r="G69" s="95"/>
-      <c r="H69" s="95"/>
-      <c r="I69" s="95"/>
-      <c r="J69" s="95"/>
-      <c r="K69" s="96"/>
+      <c r="C69" s="102"/>
+      <c r="D69" s="102"/>
+      <c r="E69" s="102"/>
+      <c r="F69" s="102"/>
+      <c r="G69" s="102"/>
+      <c r="H69" s="102"/>
+      <c r="I69" s="102"/>
+      <c r="J69" s="102"/>
+      <c r="K69" s="103"/>
       <c r="L69" s="43"/>
       <c r="M69" s="43"/>
-      <c r="N69" s="94" t="s">
+      <c r="N69" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="O69" s="95"/>
-      <c r="P69" s="95"/>
-      <c r="Q69" s="95"/>
-      <c r="R69" s="95"/>
-      <c r="S69" s="95"/>
-      <c r="T69" s="95"/>
-      <c r="U69" s="95"/>
-      <c r="V69" s="95"/>
-      <c r="W69" s="96"/>
+      <c r="O69" s="102"/>
+      <c r="P69" s="102"/>
+      <c r="Q69" s="102"/>
+      <c r="R69" s="102"/>
+      <c r="S69" s="102"/>
+      <c r="T69" s="102"/>
+      <c r="U69" s="102"/>
+      <c r="V69" s="102"/>
+      <c r="W69" s="103"/>
       <c r="X69" s="43"/>
       <c r="Y69" s="14"/>
       <c r="Z69" s="14"/>
@@ -5837,12 +5837,12 @@
     </row>
     <row r="70" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="43"/>
-      <c r="B70" s="97" t="s">
+      <c r="B70" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="C70" s="98"/>
-      <c r="D70" s="98"/>
-      <c r="E70" s="99"/>
+      <c r="C70" s="105"/>
+      <c r="D70" s="105"/>
+      <c r="E70" s="106"/>
       <c r="F70" s="43"/>
       <c r="G70" s="43"/>
       <c r="H70" s="34" t="s">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="L70" s="43"/>
       <c r="M70" s="43"/>
-      <c r="N70" s="100" t="s">
+      <c r="N70" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="O70" s="101"/>
-      <c r="P70" s="101"/>
-      <c r="Q70" s="102"/>
+      <c r="O70" s="108"/>
+      <c r="P70" s="108"/>
+      <c r="Q70" s="109"/>
       <c r="R70" s="43"/>
       <c r="S70" s="43"/>
       <c r="T70" s="34" t="s">
@@ -5903,9 +5903,7 @@
       <c r="D71" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>87</v>
-      </c>
+      <c r="E71" s="5"/>
       <c r="F71" s="43"/>
       <c r="G71" s="43"/>
       <c r="H71" s="11" t="s">
@@ -6210,7 +6208,9 @@
       <c r="B76" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="5"/>
+      <c r="C76" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="D76" s="18" t="s">
         <v>14</v>
       </c>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="85" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="43"/>
-      <c r="B85" s="103" t="s">
+      <c r="B85" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C85" s="106" t="s">
+      <c r="C85" s="97" t="s">
         <v>24</v>
       </c>
       <c r="D85" s="26" t="s">
@@ -6760,10 +6760,10 @@
       </c>
       <c r="L85" s="43"/>
       <c r="M85" s="43"/>
-      <c r="N85" s="103" t="s">
+      <c r="N85" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="O85" s="106" t="s">
+      <c r="O85" s="97" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="26" t="s">
@@ -6793,8 +6793,8 @@
     </row>
     <row r="86" spans="1:37" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="43"/>
-      <c r="B86" s="104"/>
-      <c r="C86" s="107"/>
+      <c r="B86" s="95"/>
+      <c r="C86" s="98"/>
       <c r="D86" s="18" t="s">
         <v>13</v>
       </c>
@@ -6811,8 +6811,8 @@
       </c>
       <c r="L86" s="43"/>
       <c r="M86" s="43"/>
-      <c r="N86" s="104"/>
-      <c r="O86" s="107"/>
+      <c r="N86" s="95"/>
+      <c r="O86" s="98"/>
       <c r="P86" s="18" t="s">
         <v>13</v>
       </c>
@@ -6840,8 +6840,8 @@
     </row>
     <row r="87" spans="1:37" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="43"/>
-      <c r="B87" s="104"/>
-      <c r="C87" s="108" t="s">
+      <c r="B87" s="95"/>
+      <c r="C87" s="99" t="s">
         <v>25</v>
       </c>
       <c r="D87" s="18" t="s">
@@ -6856,8 +6856,8 @@
       <c r="K87" s="54"/>
       <c r="L87" s="43"/>
       <c r="M87" s="43"/>
-      <c r="N87" s="104"/>
-      <c r="O87" s="108" t="s">
+      <c r="N87" s="95"/>
+      <c r="O87" s="99" t="s">
         <v>25</v>
       </c>
       <c r="P87" s="18" t="s">
@@ -6887,8 +6887,8 @@
     </row>
     <row r="88" spans="1:37" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="43"/>
-      <c r="B88" s="105"/>
-      <c r="C88" s="109"/>
+      <c r="B88" s="96"/>
+      <c r="C88" s="100"/>
       <c r="D88" s="27" t="s">
         <v>23</v>
       </c>
@@ -6901,8 +6901,8 @@
       <c r="K88" s="54"/>
       <c r="L88" s="43"/>
       <c r="M88" s="43"/>
-      <c r="N88" s="105"/>
-      <c r="O88" s="109"/>
+      <c r="N88" s="96"/>
+      <c r="O88" s="100"/>
       <c r="P88" s="27" t="s">
         <v>23</v>
       </c>
@@ -7512,57 +7512,57 @@
     </row>
     <row r="103" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="43"/>
-      <c r="B103" s="94" t="s">
+      <c r="B103" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="C103" s="95"/>
-      <c r="D103" s="95"/>
-      <c r="E103" s="95"/>
-      <c r="F103" s="95"/>
-      <c r="G103" s="95"/>
-      <c r="H103" s="95"/>
-      <c r="I103" s="95"/>
-      <c r="J103" s="95"/>
-      <c r="K103" s="96"/>
+      <c r="C103" s="102"/>
+      <c r="D103" s="102"/>
+      <c r="E103" s="102"/>
+      <c r="F103" s="102"/>
+      <c r="G103" s="102"/>
+      <c r="H103" s="102"/>
+      <c r="I103" s="102"/>
+      <c r="J103" s="102"/>
+      <c r="K103" s="103"/>
       <c r="L103" s="43"/>
       <c r="M103" s="43"/>
-      <c r="N103" s="94" t="s">
+      <c r="N103" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="O103" s="95"/>
-      <c r="P103" s="95"/>
-      <c r="Q103" s="95"/>
-      <c r="R103" s="95"/>
-      <c r="S103" s="95"/>
-      <c r="T103" s="95"/>
-      <c r="U103" s="95"/>
-      <c r="V103" s="95"/>
-      <c r="W103" s="96"/>
+      <c r="O103" s="102"/>
+      <c r="P103" s="102"/>
+      <c r="Q103" s="102"/>
+      <c r="R103" s="102"/>
+      <c r="S103" s="102"/>
+      <c r="T103" s="102"/>
+      <c r="U103" s="102"/>
+      <c r="V103" s="102"/>
+      <c r="W103" s="103"/>
       <c r="X103" s="43"/>
       <c r="Y103" s="43"/>
-      <c r="Z103" s="94" t="s">
+      <c r="Z103" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="AA103" s="95"/>
-      <c r="AB103" s="95"/>
-      <c r="AC103" s="95"/>
-      <c r="AD103" s="95"/>
-      <c r="AE103" s="95"/>
-      <c r="AF103" s="95"/>
-      <c r="AG103" s="95"/>
-      <c r="AH103" s="95"/>
-      <c r="AI103" s="96"/>
+      <c r="AA103" s="102"/>
+      <c r="AB103" s="102"/>
+      <c r="AC103" s="102"/>
+      <c r="AD103" s="102"/>
+      <c r="AE103" s="102"/>
+      <c r="AF103" s="102"/>
+      <c r="AG103" s="102"/>
+      <c r="AH103" s="102"/>
+      <c r="AI103" s="103"/>
       <c r="AJ103" s="43"/>
       <c r="AK103" s="14"/>
     </row>
     <row r="104" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="43"/>
-      <c r="B104" s="100" t="s">
+      <c r="B104" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="C104" s="101"/>
-      <c r="D104" s="101"/>
-      <c r="E104" s="102"/>
+      <c r="C104" s="108"/>
+      <c r="D104" s="108"/>
+      <c r="E104" s="109"/>
       <c r="F104" s="43"/>
       <c r="G104" s="43"/>
       <c r="H104" s="34" t="s">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="L104" s="43"/>
       <c r="M104" s="43"/>
-      <c r="N104" s="100" t="s">
+      <c r="N104" s="107" t="s">
         <v>118</v>
       </c>
-      <c r="O104" s="101"/>
-      <c r="P104" s="101"/>
-      <c r="Q104" s="102"/>
+      <c r="O104" s="108"/>
+      <c r="P104" s="108"/>
+      <c r="Q104" s="109"/>
       <c r="R104" s="43"/>
       <c r="S104" s="43"/>
       <c r="T104" s="34" t="s">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="X104" s="43"/>
       <c r="Y104" s="43"/>
-      <c r="Z104" s="100" t="s">
+      <c r="Z104" s="107" t="s">
         <v>119</v>
       </c>
-      <c r="AA104" s="101"/>
-      <c r="AB104" s="101"/>
-      <c r="AC104" s="102"/>
+      <c r="AA104" s="108"/>
+      <c r="AB104" s="108"/>
+      <c r="AC104" s="109"/>
       <c r="AD104" s="43"/>
       <c r="AE104" s="43"/>
       <c r="AF104" s="34" t="s">
@@ -8590,10 +8590,10 @@
     </row>
     <row r="119" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="43"/>
-      <c r="B119" s="103" t="s">
+      <c r="B119" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C119" s="106" t="s">
+      <c r="C119" s="97" t="s">
         <v>24</v>
       </c>
       <c r="D119" s="26" t="s">
@@ -8612,10 +8612,10 @@
       </c>
       <c r="L119" s="43"/>
       <c r="M119" s="43"/>
-      <c r="N119" s="103" t="s">
+      <c r="N119" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="O119" s="106" t="s">
+      <c r="O119" s="97" t="s">
         <v>24</v>
       </c>
       <c r="P119" s="26" t="s">
@@ -8630,10 +8630,10 @@
       <c r="W119" s="52"/>
       <c r="X119" s="43"/>
       <c r="Y119" s="43"/>
-      <c r="Z119" s="103" t="s">
+      <c r="Z119" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="AA119" s="106" t="s">
+      <c r="AA119" s="97" t="s">
         <v>24</v>
       </c>
       <c r="AB119" s="26" t="s">
@@ -8651,8 +8651,8 @@
     </row>
     <row r="120" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="43"/>
-      <c r="B120" s="104"/>
-      <c r="C120" s="107"/>
+      <c r="B120" s="95"/>
+      <c r="C120" s="98"/>
       <c r="D120" s="18" t="s">
         <v>13</v>
       </c>
@@ -8669,8 +8669,8 @@
       </c>
       <c r="L120" s="43"/>
       <c r="M120" s="43"/>
-      <c r="N120" s="104"/>
-      <c r="O120" s="107"/>
+      <c r="N120" s="95"/>
+      <c r="O120" s="98"/>
       <c r="P120" s="18" t="s">
         <v>13</v>
       </c>
@@ -8683,8 +8683,8 @@
       <c r="W120" s="52"/>
       <c r="X120" s="43"/>
       <c r="Y120" s="43"/>
-      <c r="Z120" s="104"/>
-      <c r="AA120" s="107"/>
+      <c r="Z120" s="95"/>
+      <c r="AA120" s="98"/>
       <c r="AB120" s="18" t="s">
         <v>13</v>
       </c>
@@ -8700,8 +8700,8 @@
     </row>
     <row r="121" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="43"/>
-      <c r="B121" s="104"/>
-      <c r="C121" s="108" t="s">
+      <c r="B121" s="95"/>
+      <c r="C121" s="99" t="s">
         <v>25</v>
       </c>
       <c r="D121" s="18" t="s">
@@ -8716,8 +8716,8 @@
       <c r="K121" s="54"/>
       <c r="L121" s="43"/>
       <c r="M121" s="43"/>
-      <c r="N121" s="104"/>
-      <c r="O121" s="108" t="s">
+      <c r="N121" s="95"/>
+      <c r="O121" s="99" t="s">
         <v>25</v>
       </c>
       <c r="P121" s="18" t="s">
@@ -8732,8 +8732,8 @@
       <c r="W121" s="52"/>
       <c r="X121" s="43"/>
       <c r="Y121" s="43"/>
-      <c r="Z121" s="104"/>
-      <c r="AA121" s="108" t="s">
+      <c r="Z121" s="95"/>
+      <c r="AA121" s="99" t="s">
         <v>25</v>
       </c>
       <c r="AB121" s="18" t="s">
@@ -8751,8 +8751,8 @@
     </row>
     <row r="122" spans="1:37" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="43"/>
-      <c r="B122" s="105"/>
-      <c r="C122" s="109"/>
+      <c r="B122" s="96"/>
+      <c r="C122" s="100"/>
       <c r="D122" s="27" t="s">
         <v>23</v>
       </c>
@@ -8765,8 +8765,8 @@
       <c r="K122" s="54"/>
       <c r="L122" s="43"/>
       <c r="M122" s="43"/>
-      <c r="N122" s="105"/>
-      <c r="O122" s="109"/>
+      <c r="N122" s="96"/>
+      <c r="O122" s="100"/>
       <c r="P122" s="27" t="s">
         <v>23</v>
       </c>
@@ -8779,8 +8779,8 @@
       <c r="W122" s="52"/>
       <c r="X122" s="43"/>
       <c r="Y122" s="43"/>
-      <c r="Z122" s="105"/>
-      <c r="AA122" s="109"/>
+      <c r="Z122" s="96"/>
+      <c r="AA122" s="100"/>
       <c r="AB122" s="27" t="s">
         <v>23</v>
       </c>
@@ -9396,43 +9396,43 @@
     </row>
     <row r="137" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="43"/>
-      <c r="B137" s="94" t="s">
+      <c r="B137" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="C137" s="95"/>
-      <c r="D137" s="95"/>
-      <c r="E137" s="95"/>
-      <c r="F137" s="95"/>
-      <c r="G137" s="95"/>
-      <c r="H137" s="95"/>
-      <c r="I137" s="95"/>
-      <c r="J137" s="95"/>
-      <c r="K137" s="96"/>
+      <c r="C137" s="102"/>
+      <c r="D137" s="102"/>
+      <c r="E137" s="102"/>
+      <c r="F137" s="102"/>
+      <c r="G137" s="102"/>
+      <c r="H137" s="102"/>
+      <c r="I137" s="102"/>
+      <c r="J137" s="102"/>
+      <c r="K137" s="103"/>
       <c r="L137" s="43"/>
       <c r="M137" s="43"/>
-      <c r="N137" s="94" t="s">
+      <c r="N137" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="O137" s="95"/>
-      <c r="P137" s="95"/>
-      <c r="Q137" s="95"/>
-      <c r="R137" s="95"/>
-      <c r="S137" s="95"/>
-      <c r="T137" s="95"/>
-      <c r="U137" s="95"/>
-      <c r="V137" s="95"/>
-      <c r="W137" s="96"/>
+      <c r="O137" s="102"/>
+      <c r="P137" s="102"/>
+      <c r="Q137" s="102"/>
+      <c r="R137" s="102"/>
+      <c r="S137" s="102"/>
+      <c r="T137" s="102"/>
+      <c r="U137" s="102"/>
+      <c r="V137" s="102"/>
+      <c r="W137" s="103"/>
       <c r="X137" s="43"/>
       <c r="Y137" s="14"/>
     </row>
     <row r="138" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="43"/>
-      <c r="B138" s="97" t="s">
+      <c r="B138" s="104" t="s">
         <v>131</v>
       </c>
-      <c r="C138" s="98"/>
-      <c r="D138" s="98"/>
-      <c r="E138" s="99"/>
+      <c r="C138" s="105"/>
+      <c r="D138" s="105"/>
+      <c r="E138" s="106"/>
       <c r="F138" s="43"/>
       <c r="G138" s="43"/>
       <c r="H138" s="71" t="s">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="L138" s="43"/>
       <c r="M138" s="43"/>
-      <c r="N138" s="100" t="s">
+      <c r="N138" s="107" t="s">
         <v>132</v>
       </c>
-      <c r="O138" s="101"/>
-      <c r="P138" s="101"/>
-      <c r="Q138" s="102"/>
+      <c r="O138" s="108"/>
+      <c r="P138" s="108"/>
+      <c r="Q138" s="109"/>
       <c r="R138" s="43"/>
       <c r="S138" s="43"/>
       <c r="T138" s="34" t="s">
@@ -10039,10 +10039,10 @@
     </row>
     <row r="153" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="43"/>
-      <c r="B153" s="103" t="s">
+      <c r="B153" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C153" s="106" t="s">
+      <c r="C153" s="97" t="s">
         <v>24</v>
       </c>
       <c r="D153" s="26" t="s">
@@ -10057,10 +10057,10 @@
       <c r="K153" s="45"/>
       <c r="L153" s="43"/>
       <c r="M153" s="43"/>
-      <c r="N153" s="103" t="s">
+      <c r="N153" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="O153" s="106" t="s">
+      <c r="O153" s="97" t="s">
         <v>24</v>
       </c>
       <c r="P153" s="26" t="s">
@@ -10078,8 +10078,8 @@
     </row>
     <row r="154" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="43"/>
-      <c r="B154" s="104"/>
-      <c r="C154" s="107"/>
+      <c r="B154" s="95"/>
+      <c r="C154" s="98"/>
       <c r="D154" s="18" t="s">
         <v>13</v>
       </c>
@@ -10092,8 +10092,8 @@
       <c r="K154" s="45"/>
       <c r="L154" s="43"/>
       <c r="M154" s="43"/>
-      <c r="N154" s="104"/>
-      <c r="O154" s="107"/>
+      <c r="N154" s="95"/>
+      <c r="O154" s="98"/>
       <c r="P154" s="18" t="s">
         <v>13</v>
       </c>
@@ -10109,8 +10109,8 @@
     </row>
     <row r="155" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="43"/>
-      <c r="B155" s="104"/>
-      <c r="C155" s="108" t="s">
+      <c r="B155" s="95"/>
+      <c r="C155" s="99" t="s">
         <v>25</v>
       </c>
       <c r="D155" s="18" t="s">
@@ -10125,8 +10125,8 @@
       <c r="K155" s="45"/>
       <c r="L155" s="43"/>
       <c r="M155" s="43"/>
-      <c r="N155" s="104"/>
-      <c r="O155" s="108" t="s">
+      <c r="N155" s="95"/>
+      <c r="O155" s="99" t="s">
         <v>25</v>
       </c>
       <c r="P155" s="18" t="s">
@@ -10144,8 +10144,8 @@
     </row>
     <row r="156" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="43"/>
-      <c r="B156" s="105"/>
-      <c r="C156" s="109"/>
+      <c r="B156" s="96"/>
+      <c r="C156" s="100"/>
       <c r="D156" s="27" t="s">
         <v>23</v>
       </c>
@@ -10158,8 +10158,8 @@
       <c r="K156" s="45"/>
       <c r="L156" s="43"/>
       <c r="M156" s="43"/>
-      <c r="N156" s="105"/>
-      <c r="O156" s="109"/>
+      <c r="N156" s="96"/>
+      <c r="O156" s="100"/>
       <c r="P156" s="27" t="s">
         <v>23</v>
       </c>
@@ -10583,36 +10583,36 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="H97:K97"/>
-    <mergeCell ref="T97:W97"/>
-    <mergeCell ref="B85:B88"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="N85:N88"/>
-    <mergeCell ref="O85:O86"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="O87:O88"/>
-    <mergeCell ref="T63:W63"/>
-    <mergeCell ref="B69:K69"/>
-    <mergeCell ref="N69:W69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="N70:Q70"/>
-    <mergeCell ref="H63:K63"/>
-    <mergeCell ref="N35:W35"/>
-    <mergeCell ref="N36:Q36"/>
-    <mergeCell ref="N51:N54"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="B35:K35"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="H165:K165"/>
+    <mergeCell ref="T165:W165"/>
+    <mergeCell ref="B137:K137"/>
+    <mergeCell ref="N137:W137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="N138:Q138"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C154"/>
+    <mergeCell ref="N153:N156"/>
+    <mergeCell ref="O153:O154"/>
+    <mergeCell ref="C155:C156"/>
+    <mergeCell ref="O155:O156"/>
+    <mergeCell ref="AF131:AI131"/>
+    <mergeCell ref="AA119:AA120"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="O121:O122"/>
+    <mergeCell ref="AA121:AA122"/>
+    <mergeCell ref="H131:K131"/>
+    <mergeCell ref="T131:W131"/>
+    <mergeCell ref="B119:B122"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="N119:N122"/>
+    <mergeCell ref="O119:O120"/>
+    <mergeCell ref="Z119:Z122"/>
+    <mergeCell ref="B103:K103"/>
+    <mergeCell ref="N103:W103"/>
+    <mergeCell ref="Z103:AI103"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="N104:Q104"/>
+    <mergeCell ref="Z104:AC104"/>
     <mergeCell ref="Z1:AI1"/>
     <mergeCell ref="T29:W29"/>
     <mergeCell ref="N1:W1"/>
@@ -10625,36 +10625,36 @@
     <mergeCell ref="AA17:AA18"/>
     <mergeCell ref="Z17:Z20"/>
     <mergeCell ref="Z2:AC2"/>
-    <mergeCell ref="B103:K103"/>
-    <mergeCell ref="N103:W103"/>
-    <mergeCell ref="Z103:AI103"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="N104:Q104"/>
-    <mergeCell ref="Z104:AC104"/>
-    <mergeCell ref="B119:B122"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="N119:N122"/>
-    <mergeCell ref="O119:O120"/>
-    <mergeCell ref="Z119:Z122"/>
-    <mergeCell ref="AF131:AI131"/>
-    <mergeCell ref="AA119:AA120"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="O121:O122"/>
-    <mergeCell ref="AA121:AA122"/>
-    <mergeCell ref="H131:K131"/>
-    <mergeCell ref="T131:W131"/>
-    <mergeCell ref="H165:K165"/>
-    <mergeCell ref="T165:W165"/>
-    <mergeCell ref="B137:K137"/>
-    <mergeCell ref="N137:W137"/>
-    <mergeCell ref="B138:E138"/>
-    <mergeCell ref="N138:Q138"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C154"/>
-    <mergeCell ref="N153:N156"/>
-    <mergeCell ref="O153:O154"/>
-    <mergeCell ref="C155:C156"/>
-    <mergeCell ref="O155:O156"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="N35:W35"/>
+    <mergeCell ref="N36:Q36"/>
+    <mergeCell ref="N51:N54"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="T63:W63"/>
+    <mergeCell ref="B69:K69"/>
+    <mergeCell ref="N69:W69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="N70:Q70"/>
+    <mergeCell ref="H63:K63"/>
+    <mergeCell ref="H97:K97"/>
+    <mergeCell ref="T97:W97"/>
+    <mergeCell ref="B85:B88"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="N85:N88"/>
+    <mergeCell ref="O85:O86"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="O87:O88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
